--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Felder" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Felder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wörterbuch'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -560,63 +562,70 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>• Blatt „Synonyme“: wie ein Feld in Hersteller-Datenblättern heißen kann (hilft beim Auslesen ohne KI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>• Spalte „ID“ bitte NICHT ändern – darüber werden die Daten gespeichert.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Farben</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Gelb (Spalte Status) = Vorschlag von Claude, bitte prüfen und auf „bestätigt“ setzen.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Quellen (Spalte „Quelle“)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>F = Filter-Auswahl Produktkonfigurator · V = bisherige EPS-Vorlage (DE/EN) · P = EPS-Datenblattpaare 200034/200161/200326 · E = Pflichtenheft</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Feld „Ausgangsspannung“: Datentyp „Bereich (von–bis)“, Einheit V. Im Datenblatt steht „0–750 V DC“; gespeichert wird zusätzlich min 0 / max 750 / V für den Filter.</t>
         </is>
@@ -7187,4 +7196,1715 @@
   <autoFilter ref="A1:D30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B141"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Feld-ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Bezeichnung im Hersteller-Datenblatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ausgangsspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Output voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Output Voltage Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Nennspannung &amp; Bereich</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nennspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>DC Ausgang Spannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>DC-Ausgangsspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Ausgangsspannungsbereich</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Gleichspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Voltage output</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Rated output voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Ausgangsstrom</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Output current</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Nennstrom &amp; Bereich</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Nennstrom</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>DC Ausgang Strom</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Rated output current</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Ausgangsleistung</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Nennleistung &amp; Bereich</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Nennleistung</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Dauerausgangsleistung</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Rated power</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Continuous output power</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Output rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>AC Eingangsspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>DC Eingangsspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Input voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Netzspannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Spannung / Phasen / Frequenz</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Mains voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>AC input voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>eingangsstrom</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsstrom</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>eingangsstrom</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Input current</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>eingangsfrequenz</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsfrequenz</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>eingangsfrequenz</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Input frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>netzanschluss</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Netzanschluss</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>netzanschluss</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Mains</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>netzanschluss</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>AC-Anschluss</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>netzanschluss</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>AC input</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>leistungsfaktor</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Leistungsfaktor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>leistungsfaktor</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Power factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>wirkungsgrad</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Wirkungsgrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>wirkungsgrad</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>wirkungsgrad</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Effizienz</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>wirkungsgrad</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Effizienz max.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Betriebstemperatur</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Operating temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Operating temperature range</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Operation temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Umgebungstemperatur</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Arbeitstemperatur</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>lagertemperatur</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Lagertemperatur</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>lagertemperatur</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Storage temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>luftfeuchtigkeit</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Luftfeuchtigkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>luftfeuchtigkeit</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Humidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>luftfeuchtigkeit</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Relative humidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>luftfeuchtigkeit</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Rel. Luftfeuchte</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>betriebshoehe</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Betriebshöhe</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>betriebshoehe</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Altitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>betriebshoehe</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Aufstellhöhe</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>kuehlung</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Kühlung</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>kuehlung</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Cooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>kuehlung</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Kühlart</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Abmessungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Abmessungen (BxHxT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Abmessungen (B x H x T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Package Dimensions (W x H x L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Dimensions (WxHxD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>abmessungen</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Maße</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>gewicht</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Gewicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>gewicht</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>gewicht</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Net weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>normen</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Normen</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>normen</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>normen</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Sicherheitszertifikate</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>normen</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Zertifizierungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>schutzklasse</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Schutzklasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>schutzklasse</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Protection class</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>ueberspannungskategorie</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Überspannungskategorie</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>ueberspannungskategorie</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Overvoltage category</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>spannungsfestigkeit_ein_aus</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Isolation Eingang/Ausgang</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>spannungsfestigkeit_ein_aus</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Isolation In-/Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>spannungsfestigkeit_ein_aus</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Isolation input/output</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>anzeige</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Anzeige</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>anzeige</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>anzeige</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Anzeige und Bedieneinheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>betriebsarten</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Betriebsarten</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>betriebsarten</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Operation modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>betriebsarten</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Operating modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>betriebsarten</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Regelart</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>klirrfaktor</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Klirrfaktor</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>klirrfaktor</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>THD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>klirrfaktor</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Total Harmonic Distortion</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>scheitelfaktor</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Scheitelfaktor</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>scheitelfaktor</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Crest factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>scheitelfaktor</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Load Crest Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsfrequenz</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Ausgangsfrequenz</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsfrequenz</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Output frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_i</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Restwelligkeit Strom</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_i</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Ripple current</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_u</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Restwelligkeit Spannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_u</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Restwelligkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_u</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Restwelligkeit U</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_u</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_u</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Output Noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_last</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Spannungsstabilität Last</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_last</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Load regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_last</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Line/Load Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_last</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Stabilität bei 0-100% Last</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_netz</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Spannungsstabilität Netz</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_netz</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Line regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>spannungsstabilitaet_netz</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Stabilität bei ±10% ∆ UAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>spannungsausregelung_last</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Spannungsausregelung Last</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>spannungsausregelung_last</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Ausregelung 10-100% Last</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>spannungsausregelung_last</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Transient response</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>anstiegszeit_spannung</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Anstiegszeit Spannung</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>anstiegszeit_spannung</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Anstiegszeit 10-90% UNenn</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>anstiegszeit_spannung</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Rise time voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>parallelschaltung</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Parallelschaltung</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>parallelschaltung</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Parallel operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>parallelschaltung</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Parallelbetrieb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>funktionsgenerator</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Funktionsgenerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>funktionsgenerator</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Function generator</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Netzrückspeisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Energy recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Energierückspeisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Artikelnummer</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Part number</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Bestellnummer</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Order code</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Best.-Nr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Art.-Nr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Modell</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B141"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wörterbuch'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7204,7 +7204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8090,24 +8090,24 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Gewicht</t>
+          <t>Package / Dimensions</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Package Dimensions</t>
         </is>
       </c>
     </row>
@@ -8119,31 +8119,31 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Net weight</t>
+          <t>Gewicht</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>gewicht</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Normen</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>gewicht</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Standards</t>
+          <t>Net weight</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Sicherheitszertifikate</t>
+          <t>Normen</t>
         </is>
       </c>
     </row>
@@ -8167,79 +8167,79 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Zertifizierungen</t>
+          <t>Standards</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Schutzklasse</t>
+          <t>Sicherheitszertifikate</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Protection class</t>
+          <t>Zertifizierungen</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>schutzklasse</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Überspannungskategorie</t>
+          <t>Schutzklasse</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>schutzklasse</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Overvoltage category</t>
+          <t>Protection class</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Isolation Eingang/Ausgang</t>
+          <t>Überspannungskategorie</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Isolation In-/Output</t>
+          <t>Overvoltage category</t>
         </is>
       </c>
     </row>
@@ -8251,31 +8251,31 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Isolation input/output</t>
+          <t>Isolation Eingang/Ausgang</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Anzeige</t>
+          <t>Isolation In-/Output</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Isolation input/output</t>
         </is>
       </c>
     </row>
@@ -8287,223 +8287,223 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Anzeige und Bedieneinheit</t>
+          <t>Anzeige</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Betriebsarten</t>
+          <t>Display</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Operation modes</t>
+          <t>Anzeige und Bedieneinheit</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Operating modes</t>
+          <t>Indicators</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Regelart</t>
+          <t>Anzeigen</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Klirrfaktor</t>
+          <t>Betriebsarten</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>THD</t>
+          <t>Operation modes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Total Harmonic Distortion</t>
+          <t>Operating modes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Scheitelfaktor</t>
+          <t>Regelart</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Crest factor</t>
+          <t>Klirrfaktor</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Load Crest Factor</t>
+          <t>THD</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Ausgangsfrequenz</t>
+          <t>Total Harmonic Distortion</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Output frequency</t>
+          <t>Scheitelfaktor</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_i</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit Strom</t>
+          <t>Crest factor</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_i</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Ripple current</t>
+          <t>Load Crest Factor</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit Spannung</t>
+          <t>Ausgangsfrequenz</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit</t>
+          <t>Output frequency</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>restwelligkeit_i</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit U</t>
+          <t>Restwelligkeit Strom</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>restwelligkeit_i</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Ripple current</t>
         </is>
       </c>
     </row>
@@ -8515,307 +8515,307 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Output Noise</t>
+          <t>Restwelligkeit Spannung</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Last</t>
+          <t>Restwelligkeit</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Load regulation</t>
+          <t>Restwelligkeit U</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Line/Load Regulation</t>
+          <t>Ripple</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Stabilität bei 0-100% Last</t>
+          <t>Output Noise</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Netz</t>
+          <t>Spannungsstabilität Last</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Line regulation</t>
+          <t>Load regulation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Stabilität bei ±10% ∆ UAC</t>
+          <t>Line/Load Regulation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Spannungsausregelung Last</t>
+          <t>Stabilität bei 0-100% Last</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Ausregelung 10-100% Last</t>
+          <t>Spannungsstabilität Netz</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Transient response</t>
+          <t>Line regulation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit Spannung</t>
+          <t>Stabilität bei ±10% ∆ UAC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit 10-90% UNenn</t>
+          <t>Spannungsausregelung Last</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Rise time voltage</t>
+          <t>Ausregelung 10-100% Last</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Parallelschaltung</t>
+          <t>Transient response</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Parallel operation</t>
+          <t>Anstiegszeit Spannung</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Parallelbetrieb</t>
+          <t>Anstiegszeit 10-90% UNenn</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>funktionsgenerator</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Funktionsgenerator</t>
+          <t>Rise time voltage</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>funktionsgenerator</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Function generator</t>
+          <t>Parallelschaltung</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Netzrückspeisung</t>
+          <t>Parallel operation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Energy recovery</t>
+          <t>Parallelbetrieb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>funktionsgenerator</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Energierückspeisung</t>
+          <t>Funktionsgenerator</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>funktionsgenerator</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Artikelnummer</t>
+          <t>Function generator</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Netzrückspeisung</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Bestellnummer</t>
+          <t>Energy recovery</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Order code</t>
+          <t>Energierückspeisung</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Best.-Nr.</t>
+          <t>Artikelnummer</t>
         </is>
       </c>
     </row>
@@ -8839,55 +8839,55 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Art.-Nr.</t>
+          <t>Part number</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Bestellnummer</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Modell</t>
+          <t>Order code</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Typ</t>
+          <t>Best.-Nr.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Art.-Nr.</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,84 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
+          <t>Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Modell</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
           <t>MODEL</t>
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Typenbezeichnung</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B141"/>
+  <autoFilter ref="A1:B147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Felder" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Felder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>

--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Felder" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Felder" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wörterbuch'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7204,7 +7204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B147"/>
+  <dimension ref="A1:B170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8786,197 +8786,473 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Netzrückspeisung</t>
+          <t>Output to chassis</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Energy recovery</t>
+          <t>Output to case</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Energierückspeisung</t>
+          <t>Ausgang zu Gehäuse</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Artikelnummer</t>
+          <t>Ausgang/Gehäuse</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Ruggedizing</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Bestellnummer</t>
+          <t>Ruggedized</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Order code</t>
+          <t>Robuste Ausführung</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Best.-Nr.</t>
+          <t>Alarm Output</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Art.-Nr.</t>
+          <t>Alarm output</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Alarmausgang</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Modell</t>
+          <t>Alarm</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Typ</t>
+          <t>Output Overload Protection</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Overload protection</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>MODEL</t>
+          <t>Überlastschutz</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Model No.</t>
+          <t>Inrush current limiting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
+          <t>einschaltstrombegrenzung</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Inrush current limitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>einschaltstrombegrenzung</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Einschaltstrombegrenzung</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>ueberhitzungsschutz</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Over temperature protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>ueberhitzungsschutz</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Overtemperature protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>ueberhitzungsschutz</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Übertemperaturschutz</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>produkttyp</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Summary description</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>beschreibung</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Product description</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>beschreibung</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Produktbeschreibung</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Netzrückspeisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Energy recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>netzrueckspeisung</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Energierückspeisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Artikelnummer</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Part number</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Bestellnummer</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Order code</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Best.-Nr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_bestellnummer</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Art.-Nr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
           <t>hersteller_typ</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Modell</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
         <is>
           <t>Typenbezeichnung</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B147"/>
+  <autoFilter ref="A1:B170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -11,13 +11,15 @@
     <sheet name="Felder" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Synonyme" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Formulierungen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Synonyme" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wörterbuch'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Synonyme'!$A$1:$B$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Formulierungen'!$A$1:$C$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Synonyme'!$A$1:$B$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -555,77 +557,84 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• Blatt „Wörterbuch“: Übersetzungen ergänzen oder korrigieren.</t>
+          <t>• Blatt „Wörterbuch“: Übersetzungen ganzer Werte ergänzen oder korrigieren.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• Blatt „Synonyme“: wie ein Feld in Hersteller-Datenblättern heißen kann (hilft beim Auslesen ohne KI).</t>
+          <t>• Blatt „Formulierungen“: Textbausteine innerhalb eines Werts (z. B. „at full load“ = „bei Volllast“). Gilt in beide Richtungen.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>• Blatt „Synonyme“: wie ein Feld in Hersteller-Datenblättern heißen kann (hilft beim Auslesen ohne KI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>• Spalte „ID“ bitte NICHT ändern – darüber werden die Daten gespeichert.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Farben</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Gelb (Spalte Status) = Vorschlag von Claude, bitte prüfen und auf „bestätigt“ setzen.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Quellen (Spalte „Quelle“)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>F = Filter-Auswahl Produktkonfigurator · V = bisherige EPS-Vorlage (DE/EN) · P = EPS-Datenblattpaare 200034/200161/200326 · E = Pflichtenheft</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Feld „Ausgangsspannung“: Datentyp „Bereich (von–bis)“, Einheit V. Im Datenblatt steht „0–750 V DC“; gespeichert wird zusätzlich min 0 / max 750 / V für den Filter.</t>
         </is>
@@ -7204,6 +7213,1038 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>from no load to full load</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>von Leerlauf bis Volllast</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>at full load</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>bei Volllast</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>10× in den Beispielen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>at 90% load</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>bei 90% Last</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>at no load</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>im Leerlauf</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>full load</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Volllast</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>no load</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Leerlauf</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>operating range</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Betriebsbereich</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>dauerhaft</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>z. B. 3000 W continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>max per phase</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>max. pro Phase</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>per phase</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>pro Phase</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>for full specifications</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>bei voller Spezifikation</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>for full specification</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>bei voller Spezifikation</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>baseplate temperature</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Grundplattentemperatur</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>less than</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>kleiner als</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>better than</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>besser als</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>greater than</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>größer als</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>more than</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>mehr als</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>approximately</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ca.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>approx.</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>ca.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>approx</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>ca.</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>maximum</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>maximal</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>minimum</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>typical</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>typisch</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>nominal</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>nominal</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>bleibt gleich (deutsch korrekt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>non-condensing</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>nicht kondensierend</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>non condensing</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>nicht kondensierend</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>current limiting with short circuit protection</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Strombegrenzung mit Kurzschlussschutz</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>thermal shutdown with automatic recovery</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>thermische Abschaltung mit automatischem Wiederanlauf</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>thermal shutdown</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>thermische Abschaltung</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>automatic recovery</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>automatischer Wiederanlauf</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>inrush current limiting</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Einschaltstrombegrenzung</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>current limiting</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Strombegrenzung</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>short circuit protection</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Kurzschlussschutz</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>short circuit proof</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>kurzschlussfest</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>overvoltage protection</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Überspannungsschutz</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>overtemperature protection</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Übertemperaturschutz</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>not installed</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>nicht vorhanden</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>keine</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>air forced circulation with automatic fan speed regulation</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>forcierte Luftkühlung mit automatischer Lüfterdrehzahlregelung</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>air forced circulation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>forcierte Luftkühlung</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>by built-in high quality internal fans</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>durch eingebaute hochwertige Lüfter</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>by built-in high quality fans</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>durch eingebaute hochwertige Lüfter</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>temperature controlled fans</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>temperaturgeregelte Lüfter</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>natural convection</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>natürliche Konvektion</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>water cooling</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Wasserkühlung</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>cooling slots</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Lüftungsschlitze</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>high frequency ripple is less than</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>HF-Restwelligkeit kleiner als</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>high frequency ripple is better than</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>HF-Restwelligkeit besser als</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Bandbreite</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>z. B. (20 MHz BW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>designed to meet</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>ausgelegt nach</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>and corresponding standards</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>und entsprechenden Normen</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>conformal coating</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Schutzlackierung</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>ruggedized</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>robuste Ausführung</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>ruggedizing</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>robuste Ausführung</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>chassis mount</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Chassismontage</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>rackmount</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Rack-Einbau</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>rack mount</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Rack-Einbau</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>output is floating</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Ausgang potentialfrei</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>potentialfrei</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>galvanically isolated</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>galvanisch getrennt</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>adjustable</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>einstellbar</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>programmable</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>programmierbar</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>remote sensing</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Fernfühlung</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>output to chassis</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Ausgang zu Gehäuse</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>input to chassis</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Eingang zu Gehäuse</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>input to output</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Eingang zu Ausgang</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>industrial quality sine wave inverter</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Sinus-Wechselrichter in Industriequalität</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>industrial quality frequency converter</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Frequenzumformer in Industriequalität</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>sine wave inverter</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Sinus-Wechselrichter</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>frequency converter</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Frequenzumformer</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>DC/DC converter</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>DC/DC-Wandler</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>industrial quality</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Industriequalität</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>in case of insufficient cooling</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>bei unzureichender Kühlung</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>up to</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>bis zu</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>z. B. „UL 458 and EN 60950-1“</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C76"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/katalog/feldkatalog.xlsx
+++ b/katalog/feldkatalog.xlsx
@@ -11,15 +11,17 @@
     <sheet name="Felder" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Auswahlwerte" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Wörterbuch" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Formulierungen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Synonyme" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bezeichnungen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Formulierungen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Synonyme" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Felder'!$A$1:$L$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Auswahlwerte'!$A$1:$E$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wörterbuch'!$A$1:$D$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Formulierungen'!$A$1:$C$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Synonyme'!$A$1:$B$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bezeichnungen'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Formulierungen'!$A$1:$C$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Synonyme'!$A$1:$B$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -564,77 +566,84 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• Blatt „Formulierungen“: Textbausteine innerhalb eines Werts (z. B. „at full load“ = „bei Volllast“). Gilt in beide Richtungen.</t>
+          <t>• Blatt „Bezeichnungen“: andere Feldbezeichnung je Gerätetyp im EPS-Datenblatt (z. B. Lasten: „Eingangsspannung (Lastseite)“).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• Blatt „Synonyme“: wie ein Feld in Hersteller-Datenblättern heißen kann (hilft beim Auslesen ohne KI).</t>
+          <t>• Blatt „Formulierungen“: Textbausteine innerhalb eines Werts (z. B. „at full load“ = „bei Volllast“). Gilt in beide Richtungen.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>• Blatt „Synonyme“: wie ein Feld in Hersteller-Datenblättern heißen kann (hilft beim Auslesen ohne KI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>• Spalte „ID“ bitte NICHT ändern – darüber werden die Daten gespeichert.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Farben</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Hellblau = eines der 18 Kernfelder (müssen in Weclapp in jedem Fall stimmen, Pflichtprüfung in der Prüfmaske).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Gelb (Spalte Status) = Vorschlag von Claude, bitte prüfen und auf „bestätigt“ setzen.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Quellen (Spalte „Quelle“)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>F = Filter-Auswahl Produktkonfigurator · V = bisherige EPS-Vorlage (DE/EN) · P = EPS-Datenblattpaare 200034/200161/200326 · E = Pflichtenheft</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Feld „Ausgangsspannung“: Datentyp „Bereich (von–bis)“, Einheit V. Im Datenblatt steht „0–750 V DC“; gespeichert wird zusätzlich min 0 / max 750 / V für den Filter.</t>
         </is>
@@ -651,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1101,41 +1110,37 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Text wie im Datenblatt (z. B. „208–240 V AC ±10 % 1ph.“). Die Eingangsspannung wird daraus abgeleitet.</t>
+          <t>Text wie im Datenblatt (z. B. „208–240 V AC ±10 % 1ph.“). Bei AC-versorgten Geräten (AC/DC, AC/AC, Ladegeräte, Lasten).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>eingangsspannung</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Technische Daten</t>
+          <t>Allgemeine Daten</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Eingangsspannung</t>
+          <t>Netzspannung</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Input Voltage</t>
+          <t>Mains voltage</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Bereich (von–bis)</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+          <t>Mehrfachauswahl</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>ja</t>
@@ -1143,13 +1148,13 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Schieberegler</t>
+          <t>Mehrfachauswahl</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>F, V(EN)</t>
+          <t>Enton 26.10.2026</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1159,47 +1164,55 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Für den Filter; Wert aus Netzanschluss bzw. Eingangsangaben des Herstellers.</t>
+          <t>Konfigurator-Filter für AC-versorgte Geräte; wird aus dem Netzanschluss vorgeschlagen. Entfällt bei DC/DC und DC/AC.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>eingangsfrequenz</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Allgemeine Daten</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Eingangsfrequenz</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Input frequency</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>eingangsspannung</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Technische Daten</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Eingangsspannung</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Input Voltage</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Bereich (von–bis)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Schieberegler</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>F, V(EN)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1207,12 +1220,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Nur DC-Eingang (DC/DC, DC/AC), z. B. 10–800 VDC. Bei AC-Geräten steht die Versorgung in Netzanschluss/Netzspannung.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>leistungsfaktor</t>
+          <t>eingangsfrequenz</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1222,12 +1239,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Leistungsfaktor</t>
+          <t>Eingangsfrequenz</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Power factor</t>
+          <t>Input frequency</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1235,7 +1252,11 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
@@ -1252,46 +1273,38 @@
       <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>netzrueckspeisung</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>leistungsfaktor</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Netzrückspeisung</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Power feed back</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Leistungsfaktor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Power factor</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1304,7 +1317,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>bidirektional</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1314,12 +1327,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Bidirektional</t>
+          <t>Netzrückspeisung</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Bidirectional</t>
+          <t>Power feed back</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1341,24 +1354,20 @@
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>F, P</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Im englischen Datenblatt bisher als „Behavior: Bidirectional“ (200326); im deutschen fehlte die Zeile.</t>
-        </is>
-      </c>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>bidirektional</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1368,17 +1377,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Anzeige</t>
+          <t>Bidirektional</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Bidirectional</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -1389,55 +1398,63 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Dropdown</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr"/>
+          <t>F, P</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Im englischen Datenblatt bisher als „Behavior: Bidirectional“ (200326); im deutschen fehlte die Zeile.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>spannungsaufloesung</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>anzeige</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Spannungsauflösung</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Voltage resolution</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Anzeige</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1454,7 +1471,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>spannungsgenauigkeit</t>
+          <t>spannungsaufloesung</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1464,12 +1481,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Spannungsgenauigkeit</t>
+          <t>Spannungsauflösung</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Voltage accuracy</t>
+          <t>Voltage resolution</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1479,7 +1496,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
@@ -1500,7 +1517,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>spannungsgenauigkeit</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1510,12 +1527,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Last</t>
+          <t>Spannungsgenauigkeit</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Voltage stability load</t>
+          <t>Voltage accuracy</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1546,7 +1563,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1556,12 +1573,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Netz</t>
+          <t>Spannungsstabilität Last</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Voltage stability mains</t>
+          <t>Voltage stability load</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1592,7 +1609,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1602,12 +1619,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Spannungsausregelung Last</t>
+          <t>Spannungsstabilität Netz</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Response time voltage</t>
+          <t>Voltage stability mains</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1617,7 +1634,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
@@ -1625,7 +1642,7 @@
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>V, F, P</t>
+          <t>V, F</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1638,7 +1655,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1648,12 +1665,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit Spannung</t>
+          <t>Spannungsausregelung Last</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Rise time voltage</t>
+          <t>Response time voltage</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1671,7 +1688,7 @@
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
+          <t>V, F, P</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1684,7 +1701,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>stromaufloesung</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1694,12 +1711,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Stromauflösung</t>
+          <t>Anstiegszeit Spannung</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Current resolution</t>
+          <t>Rise time voltage</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1709,7 +1726,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1730,7 +1747,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>stromgenauigkeit</t>
+          <t>stromaufloesung</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1740,12 +1757,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Stromgenauigkeit</t>
+          <t>Stromauflösung</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Current accuracy</t>
+          <t>Current resolution</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1755,7 +1772,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
@@ -1776,7 +1793,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>stromstabilitaet_last</t>
+          <t>stromgenauigkeit</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1786,12 +1803,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Stromstabilität Last</t>
+          <t>Stromgenauigkeit</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Current stability load</t>
+          <t>Current accuracy</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1822,7 +1839,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>stromstabilitaet_netz</t>
+          <t>stromstabilitaet_last</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1832,12 +1849,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Stromstabilität Netz</t>
+          <t>Stromstabilität Last</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Current stability mains</t>
+          <t>Current stability load</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1868,7 +1885,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>stromausregelung</t>
+          <t>stromstabilitaet_netz</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1878,12 +1895,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Stromausregelung</t>
+          <t>Stromstabilität Netz</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Response time current</t>
+          <t>Current stability mains</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1893,7 +1910,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1901,24 +1918,20 @@
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Nur in der Filter-Auswahl; englische Bezeichnung neu vorgeschlagen.</t>
-        </is>
-      </c>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_strom</t>
+          <t>stromausregelung</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1928,12 +1941,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit Strom</t>
+          <t>Stromausregelung</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Rise time current</t>
+          <t>Response time current</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1951,20 +1964,24 @@
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Nur in der Filter-Auswahl; englische Bezeichnung neu vorgeschlagen.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>begrenzung_ausgangsstrom</t>
+          <t>anstiegszeit_strom</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1974,20 +1991,24 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Begrenzung Ausgangsstrom</t>
+          <t>Anstiegszeit Strom</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Output current limitation</t>
+          <t>Rise time current</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
@@ -2006,7 +2027,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>eingangsstrombegrenzung</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2016,12 +2037,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Eingangsstrombegrenzung</t>
+          <t>Begrenzung Ausgangsstrom</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Input current limitation</t>
+          <t>Output current limitation</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2035,24 +2056,20 @@
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>V(EN)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Bisher nur in der englischen Vorlage. Prüfen: identisch mit „Einschaltstrombegrenzung“?</t>
-        </is>
-      </c>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>einschaltstrombegrenzung</t>
+          <t>eingangsstrombegrenzung</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2062,12 +2079,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Einschaltstrombegrenzung</t>
+          <t>Eingangsstrombegrenzung</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Inrush current limitation</t>
+          <t>Input current limitation</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2081,7 +2098,7 @@
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>V(EN)</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -2091,14 +2108,14 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Nur in der Filter-Auswahl; englische Bezeichnung neu vorgeschlagen.</t>
+          <t>Bisher nur in der englischen Vorlage. Prüfen: identisch mit „Einschaltstrombegrenzung“?</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>leistungsgenauigkeit</t>
+          <t>einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2108,43 +2125,43 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Leistungsgenauigkeit</t>
+          <t>Einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Power accuracy</t>
+          <t>Inrush current limitation</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Nur in der Filter-Auswahl; englische Bezeichnung neu vorgeschlagen.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>innenwiderstandsregelung</t>
+          <t>leistungsgenauigkeit</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2154,20 +2171,24 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Innenwiderstandsregelung</t>
+          <t>Leistungsgenauigkeit</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Internal resistance regulation</t>
+          <t>Power accuracy</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr"/>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
@@ -2181,16 +2202,12 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Ja/Nein für den Filter, Zusatztext (z. B. „+Simulation“) bleibt fürs Datenblatt.</t>
-        </is>
-      </c>
+      <c r="L32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>innenwiderstandsregelung</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2200,17 +2217,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Überspannungskategorie</t>
+          <t>Innenwiderstandsregelung</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Overvoltage category</t>
+          <t>Internal resistance regulation</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
@@ -2227,12 +2244,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein für den Filter, Zusatztext (z. B. „+Simulation“) bleibt fürs Datenblatt.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ueberhitzungsschutz</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2242,17 +2263,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Überhitzungsschutz</t>
+          <t>Überspannungskategorie</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Overheat protection</t>
+          <t>Overvoltage category</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -2274,7 +2295,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>ueberhitzungsschutz</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2284,30 +2305,26 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Spannungsfestigkeit Eingang zu Ausgang</t>
+          <t>Überhitzungsschutz</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Isolation input/output</t>
+          <t>Overheat protection</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V, F</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2320,7 +2337,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_aus_geh</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2330,12 +2347,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Spannungsfestigkeit Ausgang zu Gehäuse</t>
+          <t>Spannungsfestigkeit Eingang zu Ausgang</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Isolation output/enclosure</t>
+          <t>Isolation input/output</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2366,7 +2383,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2376,26 +2393,30 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Schutzklasse</t>
+          <t>Spannungsfestigkeit Ausgang zu Gehäuse</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Protection class</t>
+          <t>Isolation output/enclosure</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr"/>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2408,7 +2429,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>reihenschaltung</t>
+          <t>schutzklasse</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2418,17 +2439,17 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Reihenschaltung</t>
+          <t>Schutzklasse</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Series operation</t>
+          <t>Protection class</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
@@ -2437,24 +2458,20 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Englische Zeile fehlte bisher. Bis zur Klärung (Chef-Punkt 2) getrennt von Master-Slave Reihenschaltung.</t>
-        </is>
-      </c>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>master_slave_reihenschaltung</t>
+          <t>reihenschaltung</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2464,12 +2481,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Master-Slave Reihenschaltung</t>
+          <t>Reihenschaltung</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Master-slave series operation</t>
+          <t>Series operation</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2483,7 +2500,7 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -2493,89 +2510,93 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Chef-Punkt 2: identisch mit „Reihenschaltung“?</t>
+          <t>Englische Zeile fehlte bisher. Bis zur Klärung (Chef-Punkt 2) getrennt von Master-Slave Reihenschaltung.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>parallelschaltung</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>master_slave_reihenschaltung</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Parallelschaltung</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Parallel operation</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Master-Slave Reihenschaltung</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Master-slave series operation</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Chef-Punkt 2: identisch mit „Reihenschaltung“?</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>current_sharing</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>parallelschaltung</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Current Sharing</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Current sharing</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Parallelschaltung</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Parallel operation</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -2590,42 +2611,34 @@
       <c r="L41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>kuehlung</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>current_sharing</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Kühlung</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Cooling</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Current Sharing</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Current sharing</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -2642,7 +2655,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2652,24 +2665,20 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Betriebstemperatur</t>
+          <t>Kühlung</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Operating temperature</t>
+          <t>Cooling</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Bereich (von–bis)</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
           <t>ja</t>
@@ -2677,7 +2686,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Schieberegler</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
@@ -2691,45 +2700,49 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>Bisher EN „Operation temperature“.</t>
-        </is>
-      </c>
+      <c r="L43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>lagertemperatur</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Lagertemperatur</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Storage temperature</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Betriebstemperatur</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Operating temperature</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Schieberegler</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -2741,12 +2754,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Bisher EN „Operation temperature“.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>luftfeuchtigkeit</t>
+          <t>lagertemperatur</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2756,22 +2773,22 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Luftfeuchtigkeit</t>
+          <t>Lagertemperatur</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Humidity</t>
+          <t>Storage temperature</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Bereich (von–bis)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
@@ -2792,7 +2809,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>betriebshoehe</t>
+          <t>luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2802,12 +2819,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Betriebshöhe</t>
+          <t>Luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Altitude</t>
+          <t>Humidity</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2817,7 +2834,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
@@ -2833,49 +2850,41 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>Bisher falsch übersetzt als „Attitude“.</t>
-        </is>
-      </c>
+      <c r="L46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>bauform</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>betriebshoehe</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Bauform</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Betriebshöhe</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Altitude</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2887,37 +2896,49 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Bisher falsch übersetzt als „Attitude“.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>normen</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>bauform</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Normen</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Standards</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Bauform</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -2934,7 +2955,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -2944,17 +2965,17 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Robuste Ausführung</t>
+          <t>Normen</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Ruggedized</t>
+          <t>Standards</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
@@ -2963,24 +2984,20 @@
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>V(EN)</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>Bisher nur in der englischen Vorlage („ruggedized“).</t>
-        </is>
-      </c>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>power_fail</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -2990,12 +3007,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Power fail</t>
+          <t>Robuste Ausführung</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Power fail</t>
+          <t>Ruggedized</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3009,20 +3026,24 @@
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
+          <t>V(EN)</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Bisher nur in der englischen Vorlage („ruggedized“).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>alarmmanagement</t>
+          <t>power_fail</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -3032,12 +3053,12 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Alarmmanagement</t>
+          <t>Power fail</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Alarm management</t>
+          <t>Power fail</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3059,49 +3080,37 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Bisher EN „Alarmmanagement“ (deutsch).</t>
-        </is>
-      </c>
+      <c r="L51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>funktionsgenerator</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>alarmmanagement</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Funktionsgenerator</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Function generator</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Alarmmanagement</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Alarm management</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Ja/Nein</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Ja/Nein</t>
-        </is>
-      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr">
         <is>
@@ -3115,39 +3124,47 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein für den Filter, Zusatztext (z. B. „+arbitrary“) bleibt fürs Datenblatt.</t>
+          <t>Bisher EN „Alarmmanagement“ (deutsch).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>voreinstellung_ausgang</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>funktionsgenerator</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Allgemeine Daten</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Voreinstellung Ausgang</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Output preset</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Funktionsgenerator</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Function generator</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>Ja/Nein</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
@@ -3159,12 +3176,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein für den Filter, Zusatztext (z. B. „+arbitrary“) bleibt fürs Datenblatt.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>speicherplaetze</t>
+          <t>voreinstellung_ausgang</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -3174,17 +3195,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Speicherplätze</t>
+          <t>Voreinstellung Ausgang</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>Output preset</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
@@ -3206,7 +3227,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>innenkapazitaet</t>
+          <t>speicherplaetze</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3216,12 +3237,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Kapazität</t>
+          <t>Speicherplätze</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3229,17 +3250,13 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>µF</t>
-        </is>
-      </c>
+      <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V, F</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3250,46 +3267,42 @@
       <c r="L55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>schnittstellen</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Schnittstellen</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Schnittstellen</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Interfaces</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Mehrfachauswahl</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>Mehrfachauswahl</t>
-        </is>
-      </c>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>innenkapazitaet</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Allgemeine Daten</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Kapazität</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>µF</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -3297,62 +3310,66 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>Wird automatisch aus den Schnittstellen-Zeilen unten gebildet (Standard oder Option).</t>
-        </is>
-      </c>
+      <c r="L56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>if_analog</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>schnittstellen</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Schnittstellen</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Analoge Programmierung (isoliert)</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Analog programming (isolated)</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Schnittstelle</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Schnittstellen</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Interfaces</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Mehrfachauswahl</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Mehrfachauswahl</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Bisher DE „Analoge Programmierung ISO“, EN „Analog Isolation“.</t>
+          <t>Wird automatisch aus den Schnittstellen-Zeilen unten gebildet (Standard oder Option).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>if_usb</t>
+          <t>if_analog</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -3362,12 +3379,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>USB-Schnittstelle</t>
+          <t>Analoge Programmierung (isoliert)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>USB interface</t>
+          <t>Analog programming (isolated)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3384,17 +3401,21 @@
           <t>V, P</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Bisher DE „Analoge Programmierung ISO“, EN „Analog Isolation“.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>if_ethernet</t>
+          <t>if_usb</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3404,12 +3425,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Ethernet-Schnittstelle</t>
+          <t>USB-Schnittstelle</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Ethernet interface</t>
+          <t>USB interface</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3436,7 +3457,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>if_rs232</t>
+          <t>if_ethernet</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -3446,12 +3467,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>RS232-Schnittstelle</t>
+          <t>Ethernet-Schnittstelle</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>RS232 interface</t>
+          <t>Ethernet interface</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3478,7 +3499,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>if_rs485</t>
+          <t>if_rs232</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3488,12 +3509,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>RS485-Schnittstelle</t>
+          <t>RS232-Schnittstelle</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>RS485 interface</t>
+          <t>RS232 interface</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3507,7 +3528,7 @@
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V, P</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -3520,7 +3541,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>if_gpib</t>
+          <t>if_rs485</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -3530,12 +3551,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>GPIB-Schnittstelle</t>
+          <t>RS485-Schnittstelle</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>GPIB interface</t>
+          <t>RS485 interface</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3557,16 +3578,12 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>Bisher falsch „GBIP“.</t>
-        </is>
-      </c>
+      <c r="L62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>if_can</t>
+          <t>if_gpib</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3576,12 +3593,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>CAN-Schnittstelle</t>
+          <t>GPIB-Schnittstelle</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>CAN interface</t>
+          <t>GPIB interface</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3595,7 +3612,7 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -3603,12 +3620,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Bisher falsch „GBIP“.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>if_canopen</t>
+          <t>if_can</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -3618,12 +3639,12 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>CANopen-Schnittstelle</t>
+          <t>CAN-Schnittstelle</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>CANopen interface</t>
+          <t>CAN interface</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -3637,24 +3658,20 @@
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Beispiele</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>Neu: in 5 Hersteller-PDFs genannt.</t>
-        </is>
-      </c>
+          <t>V, P</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>if_profibus</t>
+          <t>if_canopen</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3664,12 +3681,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Profibus</t>
+          <t>CANopen-Schnittstelle</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Profibus</t>
+          <t>CANopen interface</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -3683,20 +3700,24 @@
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr"/>
+          <t>Beispiele</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Neu: in 5 Hersteller-PDFs genannt.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>if_profinet</t>
+          <t>if_profibus</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -3706,12 +3727,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Profinet</t>
+          <t>Profibus</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Profinet</t>
+          <t>Profibus</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -3725,24 +3746,20 @@
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>P(EN)</t>
-        </is>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Bisher nur im englischen Datenblatt.</t>
-        </is>
-      </c>
+          <t>V, P</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>if_modbus</t>
+          <t>if_profinet</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -3752,12 +3769,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Modbus</t>
+          <t>Profinet</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Modbus</t>
+          <t>Profinet</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3788,7 +3805,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>if_ethercat</t>
+          <t>if_modbus</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -3798,12 +3815,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>EtherCAT-Schnittstelle</t>
+          <t>Modbus</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>EtherCAT interface</t>
+          <t>Modbus</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3817,20 +3834,24 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr"/>
+          <t>P(EN)</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Bisher nur im englischen Datenblatt.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>genauigkeit_schnittstelle</t>
+          <t>if_ethercat</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -3840,17 +3861,17 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Genauigkeit Schnittstelle</t>
+          <t>EtherCAT-Schnittstelle</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Interface accuracy</t>
+          <t>EtherCAT interface</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Schnittstelle</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
@@ -3872,7 +3893,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>genauigkeit_schnittstelle</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -3882,12 +3903,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Genauigkeit Schnittstelle</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Interface accuracy</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3912,316 +3933,312 @@
       <c r="L70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>software</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Schnittstellen</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>V, P</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>ausgangsspannung</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Ausgangsspannung</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>Output voltage</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Schieberegler</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>V, F</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>Filter: Wunsch +20 %, aufgerundet (bis 100: 1-2-5-Reihe, darüber 250er-Schritte), harte Obergrenze.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>ausgangsspannung_2</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Ausgangsspannung 2</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Output voltage 2</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>V(EN)</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>Vorschlag – bitte prüfen</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Bisher nur in der englischen Vorlage (Geräte mit zweitem Ausgang/Bereich).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>ausgangsstrom</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Ausgangsstrom</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Output current</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>Schieberegler</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>V, F</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>ausgangsstrom_2</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Ausgangsstrom 2</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Output current 2</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>V(EN)</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>Vorschlag – bitte prüfen</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>ausgangsleistung</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Ausgangsleistung</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>Bereich (von–bis)</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Schieberegler</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>V, F</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>eingangsstrom</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Technische Daten</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Eingangsstrom</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Input current</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Bereich (von–bis)</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>F, P</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -4234,7 +4251,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>eingangsleistung</t>
+          <t>eingangsstrom</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -4244,12 +4261,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Eingangsleistung</t>
+          <t>Eingangsstrom</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Input power</t>
+          <t>Input current</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -4259,7 +4276,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr"/>
@@ -4267,24 +4284,20 @@
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>Vorschlag – bitte prüfen</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Nur in der Filter-Auswahl.</t>
-        </is>
-      </c>
+          <t>F, P</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>wirkungsgrad</t>
+          <t>eingangsleistung</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -4294,22 +4307,22 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Wirkungsgrad</t>
+          <t>Eingangsleistung</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Input power</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Bereich (von–bis)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr"/>
@@ -4317,20 +4330,24 @@
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Nur in der Filter-Auswahl.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>wirkungsgrad</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -4340,12 +4357,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit U</t>
+          <t>Wirkungsgrad</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Ripple U</t>
+          <t>Efficiency</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -4353,7 +4370,11 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="inlineStr"/>
@@ -4372,7 +4393,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_i</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -4382,12 +4403,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit I</t>
+          <t>Restwelligkeit U</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Ripple I</t>
+          <t>Ripple U</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -4412,46 +4433,34 @@
       <c r="L80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>widerstand_einstellbereich</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>restwelligkeit_i</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Widerstand Einstellbereich</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Resistance adjustment range</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Bereich (von–bis)</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>Ω</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Schieberegler</t>
-        </is>
-      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Restwelligkeit I</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Ripple I</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
@@ -4463,45 +4472,53 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>Bisher „Widerstand Einstellbereich 1“.</t>
-        </is>
-      </c>
+      <c r="L81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>widerstand_aufloesung</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>widerstand_einstellbereich</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Widerstand Auflösung</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Resistance resolution</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr"/>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Widerstand Einstellbereich</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Resistance adjustment range</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Bereich (von–bis)</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Schieberegler</t>
+        </is>
+      </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
+          <t>V, F</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
@@ -4509,12 +4526,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Bisher „Widerstand Einstellbereich 1“.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>fernfuehlung</t>
+          <t>widerstand_aufloesung</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4524,17 +4545,17 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Fernfühlungsausregelung</t>
+          <t>Widerstand Auflösung</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Remote sensing</t>
+          <t>Resistance resolution</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
@@ -4554,50 +4575,38 @@
       <c r="L83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>ausgangsfrequenz</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>fernfuehlung</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Ausgangsfrequenz</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Output frequency</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Fernfühlungsausregelung</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
+          <t>V, P</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -4608,38 +4617,50 @@
       <c r="L84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>frequenzgenauigkeit</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>ausgangsfrequenz</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Technische Daten</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Frequenzgenauigkeit</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Frequency accuracy</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="5" t="inlineStr"/>
-      <c r="H85" s="5" t="inlineStr"/>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Ausgangsfrequenz</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Output frequency</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V, F</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -4652,7 +4673,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>frequenzgenauigkeit</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -4662,12 +4683,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Scheitelfaktor</t>
+          <t>Frequenzgenauigkeit</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Crest factor</t>
+          <t>Frequency accuracy</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -4694,7 +4715,7 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -4704,12 +4725,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Klirrfaktor (THD)</t>
+          <t>Scheitelfaktor</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Distortion (THD)</t>
+          <t>Crest factor</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4717,17 +4738,13 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="F87" s="5" t="inlineStr"/>
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>V, F</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -4740,7 +4757,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -4750,12 +4767,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Abmessungen (B × H × T)</t>
+          <t>Klirrfaktor (THD)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Dimensions (W × H × D)</t>
+          <t>Distortion (THD)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4765,7 +4782,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr"/>
@@ -4786,7 +4803,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -4796,22 +4813,22 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Gewicht</t>
+          <t>Abmessungen (B × H × T)</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Dimensions (W × H × D)</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Zahl</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -4827,94 +4844,82 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>gewicht</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Technische Daten</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Gewicht</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Zahl</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>V, F</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
         <is>
           <t>Geht zusätzlich als Artikelgewicht nach Weclapp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>bestellnummer</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Technische Daten</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Bestellnummer</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>Order code</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>SKU-Suche</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>V, F, E</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Eingabe von Hand; Dateiname d/e + Bestellnummer.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>optionen</t>
+          <t>bestellnummer</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Optionen</t>
+          <t>Technische Daten</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Optionen</t>
+          <t>Bestellnummer</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Order code</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Liste</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -4925,59 +4930,71 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
+          <t>SKU-Suche</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>V, F, E</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Eingabe von Hand; Dateiname d/e + Bestellnummer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>optionen</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Optionen</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Optionen</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Liste</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
           <t>Suchtextfeld (Optionsnummer)</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>V, F, E</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
-        </is>
-      </c>
-      <c r="L91" s="5" t="inlineStr">
-        <is>
-          <t>Je Eintrag: Optionsnummer (einheitlich, Stammliste folgt in Weclapp), EPS-Code, Beschreibung DE/EN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>lieferumfang</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Lieferumfang</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Lieferumfang</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Scope of delivery</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Liste</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="5" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>V, P</t>
+          <t>V, F, E</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
@@ -4985,45 +5002,45 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Je Eintrag: Optionsnummer (einheitlich, Stammliste folgt in Weclapp), EPS-Code, Beschreibung DE/EN.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>hersteller</t>
+          <t>lieferumfang</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Intern (nicht auf Datenblatt)</t>
+          <t>Lieferumfang</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Hersteller</t>
+          <t>Lieferumfang</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Manufacturer</t>
+          <t>Scope of delivery</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Liste</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>V, P</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -5031,16 +5048,12 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>Weclapp-Lieferantendaten; nie auf dem EPS-Datenblatt.</t>
-        </is>
-      </c>
+      <c r="L93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -5050,12 +5063,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Hersteller-Typbezeichnung</t>
+          <t>Hersteller</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Manufacturer type</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5066,7 +5079,11 @@
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
           <t>E</t>
@@ -5077,12 +5094,16 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Weclapp-Lieferantendaten; nie auf dem EPS-Datenblatt.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>hersteller_typ</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -5092,12 +5113,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Hersteller-Bestellnummer</t>
+          <t>Hersteller-Typbezeichnung</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Manufacturer order code</t>
+          <t>Manufacturer type</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5119,16 +5140,12 @@
           <t>bestätigt</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Wird beim Import auf Doppelte geprüft (Hinweis).</t>
-        </is>
-      </c>
+      <c r="L95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>haendlerware</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -5138,17 +5155,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Händlerware (Originalname + Original-PDF)</t>
+          <t>Hersteller-Bestellnummer</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Reseller product</t>
+          <t>Manufacturer order code</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
@@ -5167,14 +5184,14 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>Schalter pro Hersteller, vorbereitet für EA/Tek; aus, bis J.-D. Enkelmann freischaltet.</t>
+          <t>Wird beim Import auf Doppelte geprüft (Hinweis).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>herkunft</t>
+          <t>haendlerware</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -5184,17 +5201,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Herkunft</t>
+          <t>Händlerware (Originalname + Original-PDF)</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Reseller product</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
@@ -5213,14 +5230,14 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>Neu (Auftrag) / Altbestand</t>
+          <t>Schalter pro Hersteller, vorbereitet für EA/Tek; aus, bis J.-D. Enkelmann freischaltet.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>shop_sichtbar</t>
+          <t>herkunft</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -5230,17 +5247,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Im Shop sichtbar</t>
+          <t>Herkunft</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Visible in shop</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Ja/Nein</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
@@ -5259,14 +5276,14 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>Voreinstellung: Altbestand ja, neue Auftragsgeräte nein.</t>
+          <t>Neu (Auftrag) / Altbestand</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>bilder</t>
+          <t>shop_sichtbar</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -5276,17 +5293,17 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Produktbilder</t>
+          <t>Im Shop sichtbar</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Product images</t>
+          <t>Visible in shop</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Liste</t>
+          <t>Ja/Nein</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
@@ -5305,20 +5322,66 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
+          <t>Voreinstellung: Altbestand ja, neue Auftragsgeräte nein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>bilder</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Intern (nicht auf Datenblatt)</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Produktbilder</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Product images</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Liste</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
           <t>Von Hand hinzufügbar; Herkunft klärt der Chef (Punkt 6).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L99"/>
+  <autoFilter ref="A1:L100"/>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E299" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Text,Zahl,Bereich (von–bis),Ja/Nein,Auswahl,Mehrfachauswahl,Liste,Schnittstelle"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G299 I2:I299" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G300 I2:I300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ja,"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K299" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,Vorschlag – bitte prüfen"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5332,7 +5395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5534,17 +5597,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>technologie</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Switching</t>
+          <t>1~ 115 V</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Switching</t>
+          <t>1~ 115 V</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5554,24 +5617,24 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter (alle 3 Paare)</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>technologie</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>1~ 230 V</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>1~ 230 V</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -5581,24 +5644,24 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Vorschlag</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>1~ Weitbereich 90–264 V</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>1~ wide range 90–264 V</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -5608,24 +5671,24 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter 200034/200161/200326</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>3~ 208–230 V</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>3~ 208–230 V</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -5635,24 +5698,24 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter 200034/200161/200326</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>3~ 400 V</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>3~ 400 V</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -5662,24 +5725,24 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter 200034/200161/200326</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>3~ 480 V</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>3~ 480 V</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -5689,24 +5752,24 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter 200034/200161/200326</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>netzspannung</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>TFT-Touch-Display</t>
+          <t>Sonderspannung</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>TFT touch display</t>
+          <t>Special voltage</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -5716,24 +5779,24 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>EPS 200034, 200161</t>
+          <t>Enton 26.10.2026 (Entscheidung 2b)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>technologie</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>TFT-Display</t>
+          <t>Switching</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>TFT display</t>
+          <t>Switching</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -5743,24 +5806,24 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>EPS 200326</t>
+          <t>EPS-Datenblätter (alle 3 Paare)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>technologie</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>LCD</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -5770,24 +5833,24 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Hersteller-PDFs (häufig)</t>
+          <t>Vorschlag</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -5797,24 +5860,24 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Hersteller-PDFs</t>
+          <t>EPS-Datenblätter 200034/200161/200326</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>ohne Anzeige (nur Fernsteuerung)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>None (remote control only)</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -5824,24 +5887,24 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Vorschlag</t>
+          <t>EPS-Datenblätter 200034/200161/200326</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -5851,24 +5914,24 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Vorschlag</t>
+          <t>EPS-Datenblätter 200034/200161/200326</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -5878,24 +5941,24 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>EPS 200161 („Standard“)</t>
+          <t>EPS-Datenblätter 200034/200161/200326</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Master-Slave</t>
+          <t>TFT-Touch-Display</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Master-slave</t>
+          <t>TFT touch display</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -5905,24 +5968,24 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>EPS 200034, 200326; Plating</t>
+          <t>EPS 200034, 200161</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Lüfter</t>
+          <t>TFT-Display</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>TFT display</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -5932,24 +5995,24 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter, Absopulse („Air Forced“)</t>
+          <t>EPS 200326</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Wasser</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>LCD</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -5959,24 +6022,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Gustav Klein, EPS-Option EPS/WC</t>
+          <t>Hersteller-PDFs (häufig)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Konvektion</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Convection</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -5986,24 +6049,24 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Vorschlag</t>
+          <t>Hersteller-PDFs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>bauform</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>19 Zoll</t>
+          <t>ohne Anzeige (nur Fernsteuerung)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>19 inch</t>
+          <t>None (remote control only)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -6013,24 +6076,24 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>EPS 200034, 200326; Absopulse, M.C.B</t>
+          <t>Vorschlag</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>bauform</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -6040,24 +6103,24 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>EPS 200161</t>
+          <t>Vorschlag</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>bauform</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -6067,24 +6130,24 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>M.C.B („Mini Tower“)</t>
+          <t>EPS 200161 („Standard“)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>bauform</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Schrank</t>
+          <t>Master-Slave</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Master-slave</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -6094,24 +6157,24 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Gustav Klein, Plating</t>
+          <t>EPS 200034, 200326; Plating</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>bauform</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Einbaumodul</t>
+          <t>Lüfter</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -6121,24 +6184,24 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Vorschlag</t>
+          <t>EPS-Datenblätter, Absopulse („Air Forced“)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Wasser</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -6148,24 +6211,24 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>alle DC-Geräte</t>
+          <t>Gustav Klein, EPS-Option EPS/WC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>50 Hz</t>
+          <t>Konvektion</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>50 Hz</t>
+          <t>Convection</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -6175,24 +6238,24 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>SHT, Gustav Klein</t>
+          <t>Vorschlag</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>bauform</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>60 Hz</t>
+          <t>19 Zoll</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>60 Hz</t>
+          <t>19 inch</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -6202,24 +6265,24 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>SHT</t>
+          <t>EPS 200034, 200326; Absopulse, M.C.B</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>bauform</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>50/60 Hz</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>50/60 Hz</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -6229,24 +6292,24 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>SHT, Gustav Klein</t>
+          <t>EPS 200161</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>bauform</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>400 Hz</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>400 Hz</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -6256,24 +6319,24 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Absopulse (FTP 400 Hz)</t>
+          <t>M.C.B („Mini Tower“)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>bauform</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>einstellbar</t>
+          <t>Schrank</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>adjustable</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -6283,24 +6346,24 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>SHT („40–70 Hz“)</t>
+          <t>Gustav Klein, Plating</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>bauform</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Einbaumodul</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -6310,24 +6373,24 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („2“)</t>
+          <t>Vorschlag</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -6337,24 +6400,24 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („2“)</t>
+          <t>alle DC-Geräte</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50 Hz</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50 Hz</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -6364,24 +6427,24 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („2“)</t>
+          <t>SHT, Gustav Klein</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60 Hz</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60 Hz</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -6391,24 +6454,24 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („2“)</t>
+          <t>SHT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50/60 Hz</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50/60 Hz</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -6418,24 +6481,24 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („1“)</t>
+          <t>SHT, Gustav Klein</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>400 Hz</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>400 Hz</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -6445,24 +6508,24 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („1“)</t>
+          <t>Absopulse (FTP 400 Hz)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>einstellbar</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>adjustable</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -6472,78 +6535,78 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter („1“)</t>
+          <t>SHT („40–70 Hz“)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>herkunft</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Neu (Auftrag)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>New (order)</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Pflichtenheft</t>
+          <t>EPS-Datenblätter („2“)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>herkunft</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Altbestand</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Existing stock</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>bestätigt</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Pflichtenheft</t>
+          <t>EPS-Datenblätter („2“)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Schnittstelle (alle if_*)</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -6553,24 +6616,24 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter; bei „Option“ zusätzlich EPS-Optionscode</t>
+          <t>EPS-Datenblätter („2“)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Schnittstelle (alle if_*)</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -6580,41 +6643,230 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>EPS-Datenblätter; bei „Option“ zusätzlich EPS-Optionscode</t>
+          <t>EPS-Datenblätter („2“)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>schutzklasse</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>EPS-Datenblätter („1“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>schutzklasse</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>EPS-Datenblätter („1“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>schutzklasse</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>EPS-Datenblätter („1“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>herkunft</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Neu (Auftrag)</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>New (order)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Pflichtenheft</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>herkunft</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Altbestand</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Existing stock</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>bestätigt</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Pflichtenheft</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>Schnittstelle (alle if_*)</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>EPS-Datenblätter; bei „Option“ zusätzlich EPS-Optionscode</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Schnittstelle (alle if_*)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Vorschlag – bitte prüfen</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>EPS-Datenblätter; bei „Option“ zusätzlich EPS-Optionscode</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Schnittstelle (alle if_*)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Vorschlag – bitte prüfen</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>EPS-Datenblätter; bei „Option“ zusätzlich EPS-Optionscode</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E54"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,Vorschlag – bitte prüfen"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7213,6 +7465,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Gerätetyp</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Feld-ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Bezeichnung DE</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Bezeichnung EN</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsspannung (Lastseite)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Input voltage (load side)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Entscheidung 1a: Lasten nutzen die Ausgangsfelder</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsstrom (Lastseite)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Input current (load side)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsleistung</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsleistung (Lastseite)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Input power (load side)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsspannung_2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsspannung 2 (Lastseite)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Input voltage 2 (load side)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ausgangsstrom_2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Eingangsstrom 2 (Lastseite)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Input current 2 (load side)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Elektronische Last</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>eingangsstrom</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Versorgungsstrom</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Supply current</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Netzseite der Last</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8239,13 +8686,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B170"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8759,360 +9206,360 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>leistungsfaktor</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Leistungsfaktor</t>
+          <t>Supply voltage</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>leistungsfaktor</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Power factor</t>
+          <t>Versorgungsspannung</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>wirkungsgrad</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Wirkungsgrad</t>
+          <t>AC supply</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>wirkungsgrad</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Mains voltage</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>wirkungsgrad</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Effizienz</t>
+          <t>Netzspannung</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>wirkungsgrad</t>
+          <t>netzanschluss</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Effizienz max.</t>
+          <t>Mains supply</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>leistungsfaktor</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Betriebstemperatur</t>
+          <t>Leistungsfaktor</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>leistungsfaktor</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Operating temperature</t>
+          <t>Power factor</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>wirkungsgrad</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Operating temperature range</t>
+          <t>Wirkungsgrad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>wirkungsgrad</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Operation temperature</t>
+          <t>Efficiency</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>wirkungsgrad</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Umgebungstemperatur</t>
+          <t>Effizienz</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>betriebstemperatur</t>
+          <t>wirkungsgrad</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Arbeitstemperatur</t>
+          <t>Effizienz max.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>lagertemperatur</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Lagertemperatur</t>
+          <t>Betriebstemperatur</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>lagertemperatur</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Storage temperature</t>
+          <t>Operating temperature</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>luftfeuchtigkeit</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Luftfeuchtigkeit</t>
+          <t>Operating temperature range</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>luftfeuchtigkeit</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Humidity</t>
+          <t>Operation temperature</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>luftfeuchtigkeit</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Relative humidity</t>
+          <t>Umgebungstemperatur</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>luftfeuchtigkeit</t>
+          <t>betriebstemperatur</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Rel. Luftfeuchte</t>
+          <t>Arbeitstemperatur</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>betriebshoehe</t>
+          <t>lagertemperatur</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Betriebshöhe</t>
+          <t>Lagertemperatur</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>betriebshoehe</t>
+          <t>lagertemperatur</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Altitude</t>
+          <t>Storage temperature</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>betriebshoehe</t>
+          <t>luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Aufstellhöhe</t>
+          <t>Luftfeuchtigkeit</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Kühlung</t>
+          <t>Humidity</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Cooling</t>
+          <t>Relative humidity</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>kuehlung</t>
+          <t>luftfeuchtigkeit</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Kühlart</t>
+          <t>Rel. Luftfeuchte</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>betriebshoehe</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Abmessungen</t>
+          <t>Betriebshöhe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>betriebshoehe</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Abmessungen (BxHxT)</t>
+          <t>Altitude</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>betriebshoehe</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Abmessungen (B x H x T)</t>
+          <t>Aufstellhöhe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Dimensions</t>
+          <t>Kühlung</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Package Dimensions (W x H x L)</t>
+          <t>Cooling</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>abmessungen</t>
+          <t>kuehlung</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Dimensions (WxHxD)</t>
+          <t>Kühlart</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9571,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Maße</t>
+          <t>Abmessungen</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9583,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Package / Dimensions</t>
+          <t>Abmessungen (BxHxT)</t>
         </is>
       </c>
     </row>
@@ -9148,1135 +9595,1135 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Package Dimensions</t>
+          <t>Abmessungen (B x H x T)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Gewicht</t>
+          <t>Dimensions</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Package Dimensions (W x H x L)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>gewicht</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Net weight</t>
+          <t>Dimensions (WxHxD)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Normen</t>
+          <t>Maße</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Standards</t>
+          <t>Package / Dimensions</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>abmessungen</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Sicherheitszertifikate</t>
+          <t>Package Dimensions</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>normen</t>
+          <t>gewicht</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Zertifizierungen</t>
+          <t>Gewicht</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>gewicht</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Schutzklasse</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>schutzklasse</t>
+          <t>gewicht</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Protection class</t>
+          <t>Net weight</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Überspannungskategorie</t>
+          <t>Normen</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ueberspannungskategorie</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Overvoltage category</t>
+          <t>Standards</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Isolation Eingang/Ausgang</t>
+          <t>Sicherheitszertifikate</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>normen</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Isolation In-/Output</t>
+          <t>Zertifizierungen</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_ein_aus</t>
+          <t>schutzklasse</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Isolation input/output</t>
+          <t>Schutzklasse</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>schutzklasse</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Anzeige</t>
+          <t>Protection class</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Überspannungskategorie</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>ueberspannungskategorie</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Anzeige und Bedieneinheit</t>
+          <t>Overvoltage category</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Indicators</t>
+          <t>Isolation Eingang/Ausgang</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>anzeige</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Anzeigen</t>
+          <t>Isolation In-/Output</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>spannungsfestigkeit_ein_aus</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Betriebsarten</t>
+          <t>Isolation input/output</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Operation modes</t>
+          <t>Anzeige</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Operating modes</t>
+          <t>Display</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>betriebsarten</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Regelart</t>
+          <t>Anzeige und Bedieneinheit</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Klirrfaktor</t>
+          <t>Indicators</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>anzeige</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>THD</t>
+          <t>Anzeigen</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>klirrfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Total Harmonic Distortion</t>
+          <t>Betriebsarten</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Scheitelfaktor</t>
+          <t>Operation modes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Crest factor</t>
+          <t>Operating modes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>scheitelfaktor</t>
+          <t>betriebsarten</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Load Crest Factor</t>
+          <t>Regelart</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Ausgangsfrequenz</t>
+          <t>Klirrfaktor</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ausgangsfrequenz</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Output frequency</t>
+          <t>THD</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_i</t>
+          <t>klirrfaktor</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit Strom</t>
+          <t>Total Harmonic Distortion</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_i</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Ripple current</t>
+          <t>Scheitelfaktor</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit Spannung</t>
+          <t>Crest factor</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>scheitelfaktor</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit</t>
+          <t>Load Crest Factor</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Restwelligkeit U</t>
+          <t>Ausgangsfrequenz</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>ausgangsfrequenz</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Output frequency</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>restwelligkeit_u</t>
+          <t>restwelligkeit_i</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Output Noise</t>
+          <t>Restwelligkeit Strom</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_i</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Last</t>
+          <t>Ripple current</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Load regulation</t>
+          <t>Restwelligkeit Spannung</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Line/Load Regulation</t>
+          <t>Restwelligkeit</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_last</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Stabilität bei 0-100% Last</t>
+          <t>Restwelligkeit U</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Spannungsstabilität Netz</t>
+          <t>Ripple</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>restwelligkeit_u</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Line regulation</t>
+          <t>Output Noise</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>spannungsstabilitaet_netz</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Stabilität bei ±10% ∆ UAC</t>
+          <t>Spannungsstabilität Last</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Spannungsausregelung Last</t>
+          <t>Load regulation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Ausregelung 10-100% Last</t>
+          <t>Line/Load Regulation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>spannungsausregelung_last</t>
+          <t>spannungsstabilitaet_last</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Transient response</t>
+          <t>Stabilität bei 0-100% Last</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit Spannung</t>
+          <t>Spannungsstabilität Netz</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Anstiegszeit 10-90% UNenn</t>
+          <t>Line regulation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>anstiegszeit_spannung</t>
+          <t>spannungsstabilitaet_netz</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Rise time voltage</t>
+          <t>Stabilität bei ±10% ∆ UAC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Parallelschaltung</t>
+          <t>Spannungsausregelung Last</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Parallel operation</t>
+          <t>Ausregelung 10-100% Last</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>parallelschaltung</t>
+          <t>spannungsausregelung_last</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Parallelbetrieb</t>
+          <t>Transient response</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>funktionsgenerator</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Funktionsgenerator</t>
+          <t>Anstiegszeit Spannung</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>funktionsgenerator</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Function generator</t>
+          <t>Anstiegszeit 10-90% UNenn</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_aus_geh</t>
+          <t>anstiegszeit_spannung</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Output to chassis</t>
+          <t>Rise time voltage</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_aus_geh</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Output to case</t>
+          <t>Parallelschaltung</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_aus_geh</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Ausgang zu Gehäuse</t>
+          <t>Parallel operation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>spannungsfestigkeit_aus_geh</t>
+          <t>parallelschaltung</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Ausgang/Gehäuse</t>
+          <t>Parallelbetrieb</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>funktionsgenerator</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Ruggedizing</t>
+          <t>Funktionsgenerator</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>funktionsgenerator</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Ruggedized</t>
+          <t>Function generator</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>robust</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Robuste Ausführung</t>
+          <t>Output to chassis</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>alarmmanagement</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Alarm Output</t>
+          <t>Output to case</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>alarmmanagement</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Alarm output</t>
+          <t>Ausgang zu Gehäuse</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>alarmmanagement</t>
+          <t>spannungsfestigkeit_aus_geh</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Alarmausgang</t>
+          <t>Ausgang/Gehäuse</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>alarmmanagement</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>Ruggedizing</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>begrenzung_ausgangsstrom</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Output Overload Protection</t>
+          <t>Ruggedized</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>begrenzung_ausgangsstrom</t>
+          <t>robust</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Overload protection</t>
+          <t>Robuste Ausführung</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>begrenzung_ausgangsstrom</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Überlastschutz</t>
+          <t>Alarm Output</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>einschaltstrombegrenzung</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Inrush current limiting</t>
+          <t>Alarm output</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>einschaltstrombegrenzung</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Inrush current limitation</t>
+          <t>Alarmausgang</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>einschaltstrombegrenzung</t>
+          <t>alarmmanagement</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Einschaltstrombegrenzung</t>
+          <t>Alarm</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>ueberhitzungsschutz</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Over temperature protection</t>
+          <t>Output Overload Protection</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>ueberhitzungsschutz</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Overtemperature protection</t>
+          <t>Overload protection</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>ueberhitzungsschutz</t>
+          <t>begrenzung_ausgangsstrom</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Übertemperaturschutz</t>
+          <t>Überlastschutz</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>produkttyp</t>
+          <t>einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Summary description</t>
+          <t>Inrush current limiting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>beschreibung</t>
+          <t>einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Product description</t>
+          <t>Inrush current limitation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>beschreibung</t>
+          <t>einschaltstrombegrenzung</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Produktbeschreibung</t>
+          <t>Einschaltstrombegrenzung</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>ueberhitzungsschutz</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Netzrückspeisung</t>
+          <t>Over temperature protection</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>ueberhitzungsschutz</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Energy recovery</t>
+          <t>Overtemperature protection</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>netzrueckspeisung</t>
+          <t>ueberhitzungsschutz</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Energierückspeisung</t>
+          <t>Übertemperaturschutz</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>produkttyp</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Artikelnummer</t>
+          <t>Summary description</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>beschreibung</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Product description</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>beschreibung</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Bestellnummer</t>
+          <t>Produktbeschreibung</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Order code</t>
+          <t>Netzrückspeisung</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Best.-Nr.</t>
+          <t>Energy recovery</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>hersteller_bestellnummer</t>
+          <t>netzrueckspeisung</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Art.-Nr.</t>
+          <t>Energierückspeisung</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Artikelnummer</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Modell</t>
+          <t>Part number</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Typ</t>
+          <t>Bestellnummer</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Order code</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>MODEL</t>
+          <t>Best.-Nr.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>hersteller_typ</t>
+          <t>hersteller_bestellnummer</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Model No.</t>
+          <t>Art.-Nr.</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10735,84 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
+          <t>Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Modell</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Model No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>hersteller_typ</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
           <t>Typenbezeichnung</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B170"/>
+  <autoFilter ref="A1:B176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>